--- a/public/example-files/import_resources_he.xlsx
+++ b/public/example-files/import_resources_he.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bauer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\יד תמר\משאבים אפליקציה\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B563C61-F9DA-4558-8DAA-BE45E69B0FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656AAB84-2E3F-4B86-93C5-B4A5B347661C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
   <si>
     <t>דואר אלקטרוני</t>
   </si>
@@ -58,13 +58,31 @@
     <t>תיאור השירות</t>
   </si>
   <si>
-    <t>+972 52 ___ __ __</t>
-  </si>
-  <si>
     <t>+9725__________</t>
   </si>
   <si>
     <t>כתובת</t>
+  </si>
+  <si>
+    <t>רחוב קרית ספר 8, תל אביב</t>
+  </si>
+  <si>
+    <t>+972 523433434</t>
+  </si>
+  <si>
+    <t>+97252343343</t>
+  </si>
+  <si>
+    <t>0523433434</t>
+  </si>
+  <si>
+    <t>אופן קבלת השירות</t>
+  </si>
+  <si>
+    <t>ילדים</t>
+  </si>
+  <si>
+    <t>רפואי</t>
   </si>
 </sst>
 </file>
@@ -114,57 +132,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="14">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="11"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="11"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -214,21 +187,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="10"/>
       </left>
       <right/>
@@ -240,38 +198,172 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -1404,165 +1496,203 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="12.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="21.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.6640625" style="1"/>
+    <col min="2" max="2" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="17.44140625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="21.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.6" customHeight="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:9" ht="21.6" customHeight="1">
+      <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="21.45" customHeight="1">
+      <c r="A2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>0</v>
+      <c r="H2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="21.45" customHeight="1">
-      <c r="A2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="9" t="s">
+    <row r="3" spans="1:9" ht="21.45" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="21.45" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="C4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="5" t="s">
+      <c r="G4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="21.45" customHeight="1">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="I5" s="2"/>
     </row>
-    <row r="3" spans="1:8" ht="21.45" customHeight="1">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5"/>
+    <row r="6" spans="1:9" ht="21.45" customHeight="1">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="21.45" customHeight="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5"/>
+    <row r="7" spans="1:9" ht="21.45" customHeight="1">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="2"/>
     </row>
-    <row r="5" spans="1:8" ht="21.45" customHeight="1">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="5"/>
+    <row r="8" spans="1:9" ht="21.45" customHeight="1">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="2"/>
     </row>
-    <row r="6" spans="1:8" ht="21.45" customHeight="1">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="5"/>
+    <row r="9" spans="1:9" ht="21.45" customHeight="1">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="21.45" customHeight="1">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" ht="21.45" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" ht="21.45" customHeight="1">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" ht="21" customHeight="1">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="5"/>
+    <row r="10" spans="1:9" ht="21" customHeight="1">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/public/example-files/import_resources_he.xlsx
+++ b/public/example-files/import_resources_he.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>דואר אלקטרוני</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>רפואי</t>
+  </si>
+  <si>
+    <t>כתובת אתר</t>
   </si>
 </sst>
 </file>
@@ -1510,7 +1513,7 @@
     <col min="12" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21.6" customHeight="1">
+    <row r="1" spans="1:10" ht="21.6" customHeight="1">
       <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
@@ -1538,8 +1541,11 @@
       <c r="I1" s="12" t="s">
         <v>0</v>
       </c>
+      <c r="J1" s="12" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="21.45" customHeight="1">
+    <row r="2" spans="1:10" ht="21.45" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
@@ -1565,8 +1571,9 @@
       <c r="I2" s="11" t="s">
         <v>6</v>
       </c>
+      <c r="J2" s="11"/>
     </row>
-    <row r="3" spans="1:9" ht="21.45" customHeight="1">
+    <row r="3" spans="1:10" ht="21.45" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
@@ -1590,8 +1597,9 @@
         <v>16</v>
       </c>
       <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="21.45" customHeight="1">
+    <row r="4" spans="1:10" ht="21.45" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
@@ -1615,8 +1623,9 @@
         <v>17</v>
       </c>
       <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="21.45" customHeight="1">
+    <row r="5" spans="1:10" ht="21.45" customHeight="1">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="7"/>
@@ -1628,8 +1637,9 @@
         <v>12</v>
       </c>
       <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="21.45" customHeight="1">
+    <row r="6" spans="1:10" ht="21.45" customHeight="1">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1641,8 +1651,9 @@
         <v>12</v>
       </c>
       <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="21.45" customHeight="1">
+    <row r="7" spans="1:10" ht="21.45" customHeight="1">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1654,8 +1665,9 @@
         <v>12</v>
       </c>
       <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="21.45" customHeight="1">
+    <row r="8" spans="1:10" ht="21.45" customHeight="1">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1667,8 +1679,9 @@
         <v>12</v>
       </c>
       <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="21.45" customHeight="1">
+    <row r="9" spans="1:10" ht="21.45" customHeight="1">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1680,8 +1693,9 @@
         <v>12</v>
       </c>
       <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="21" customHeight="1">
+    <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1693,6 +1707,7 @@
         <v>12</v>
       </c>
       <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
